--- a/5. Other/Báo giá linh kiện/Báo giá linh kiện BH.xlsx
+++ b/5. Other/Báo giá linh kiện/Báo giá linh kiện BH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Báo giá linh kiện\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A64B60-4427-4CA0-B7AB-4E7B79869AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6841E2B2-FD83-4351-9F8F-373531C325DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1263,6 +1263,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1302,13 +1309,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1745,44 +1745,44 @@
       <c r="H5" s="65"/>
     </row>
     <row r="6" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="79" t="s">
+      <c r="A6" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="80"/>
-      <c r="C6" s="81"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
-      <c r="H6" s="82"/>
+      <c r="B6" s="83"/>
+      <c r="C6" s="84"/>
+      <c r="D6" s="84"/>
+      <c r="E6" s="84"/>
+      <c r="F6" s="84"/>
+      <c r="G6" s="84"/>
+      <c r="H6" s="85"/>
     </row>
     <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="84"/>
+      <c r="C7" s="86"/>
+      <c r="D7" s="86"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="86"/>
+      <c r="G7" s="86"/>
+      <c r="H7" s="87"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
-      <c r="B8" s="85"/>
-      <c r="C8" s="85"/>
-      <c r="D8" s="85"/>
-      <c r="E8" s="85"/>
-      <c r="F8" s="85"/>
-      <c r="G8" s="85"/>
-      <c r="H8" s="86"/>
+      <c r="B8" s="88"/>
+      <c r="C8" s="88"/>
+      <c r="D8" s="88"/>
+      <c r="E8" s="88"/>
+      <c r="F8" s="88"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="89"/>
     </row>
     <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
-      <c r="B9" s="87"/>
-      <c r="C9" s="87"/>
-      <c r="D9" s="87"/>
+      <c r="B9" s="90"/>
+      <c r="C9" s="90"/>
+      <c r="D9" s="90"/>
       <c r="E9" s="13"/>
       <c r="F9" s="17"/>
       <c r="G9" s="17"/>
@@ -3430,13 +3430,13 @@
       <c r="C78" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="D78" s="75" t="s">
+      <c r="D78" s="78" t="s">
         <v>75</v>
       </c>
       <c r="E78" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="F78" s="77">
+      <c r="F78" s="80">
         <v>1</v>
       </c>
       <c r="G78" s="35">
@@ -3454,11 +3454,11 @@
       <c r="C79" s="49" t="s">
         <v>159</v>
       </c>
-      <c r="D79" s="76"/>
+      <c r="D79" s="79"/>
       <c r="E79" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="F79" s="78"/>
+      <c r="F79" s="81"/>
       <c r="G79" s="35">
         <v>8000</v>
       </c>
@@ -3907,28 +3907,28 @@
       <c r="J97" s="8"/>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A98" s="88">
+      <c r="A98" s="75">
         <v>88</v>
       </c>
-      <c r="B98" s="90" t="s">
+      <c r="B98" s="77" t="s">
         <v>204</v>
       </c>
-      <c r="C98" s="88" t="s">
+      <c r="C98" s="75" t="s">
         <v>203</v>
       </c>
-      <c r="D98" s="88" t="s">
+      <c r="D98" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="E98" s="88" t="s">
-        <v>122</v>
-      </c>
-      <c r="F98" s="88">
-        <v>1</v>
-      </c>
-      <c r="G98" s="89">
+      <c r="E98" s="75" t="s">
+        <v>122</v>
+      </c>
+      <c r="F98" s="75">
+        <v>1</v>
+      </c>
+      <c r="G98" s="76">
         <v>110000</v>
       </c>
-      <c r="H98" s="88"/>
+      <c r="H98" s="75"/>
       <c r="I98" s="8"/>
       <c r="J98" s="8"/>
     </row>

--- a/5. Other/Báo giá linh kiện/Báo giá linh kiện BH.xlsx
+++ b/5. Other/Báo giá linh kiện/Báo giá linh kiện BH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Báo giá linh kiện\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6841E2B2-FD83-4351-9F8F-373531C325DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A70F15D-5BAF-41DE-8025-80C8B2162704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3876,7 +3876,7 @@
         <v>1</v>
       </c>
       <c r="G96" s="73">
-        <v>50000</v>
+        <v>70000</v>
       </c>
       <c r="H96" s="72"/>
       <c r="I96" s="8"/>

--- a/5. Other/Báo giá linh kiện/Báo giá linh kiện BH.xlsx
+++ b/5. Other/Báo giá linh kiện/Báo giá linh kiện BH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Báo giá linh kiện\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A70F15D-5BAF-41DE-8025-80C8B2162704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8164D67-8583-4DE4-A7D5-40420151A7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3898,7 +3898,7 @@
         <v>1</v>
       </c>
       <c r="G97" s="73">
-        <v>60000</v>
+        <v>80000</v>
       </c>
       <c r="H97" s="74" t="s">
         <v>202</v>

--- a/5. Other/Báo giá linh kiện/Báo giá linh kiện BH.xlsx
+++ b/5. Other/Báo giá linh kiện/Báo giá linh kiện BH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Báo giá linh kiện\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8164D67-8583-4DE4-A7D5-40420151A7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC78F6A9-EDEB-4E2A-B3C2-D757FCCEC46F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
